--- a/data/raw/sales/Week 33/Nexlev/other_channels.xlsx
+++ b/data/raw/sales/Week 33/Nexlev/other_channels.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B2B" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blinkit Sales" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D2C - Nexlev" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,24 +465,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FBA78981</t>
+          <t>FBA79278</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>HD-01</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>81330.60000000001</v>
+        <v>4276.32</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -491,24 +493,928 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FBA79278</t>
+          <t>FBA79332</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HD-01</t>
+          <t>HM-01</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4648.52</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FBA79474</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B0DJFH4K8B</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TIC-03</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1919.86</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FBA79483</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B0DK9NRBWJ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6335.96</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FBA79488</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B0DFCG2VGS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>KE-01</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6413.3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FBA79566</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B0DKJSCLBD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VC-05</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17098.2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FBA79590</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B0DM6BB3VT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CFM-01</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>13045.6</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FBA79811</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B0FSF1N457</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MC-01</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2401.3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FBA79819</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B0FT8R24QM</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LR-03</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>641.92</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ASIN</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sale Amount</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FBA78980</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B0CDPMX152</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GS-02</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16093</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FBA78981</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SC-01</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21294</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FBA79263</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MR-01</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8697</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FBA79266</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B0D2LGR3GG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>T-01</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1998</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FBA79268</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B0D383WQPB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GS-05</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7996</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FBA79279</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B0D8445KJN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LR-01</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" t="n">
+        <v>13485</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FBA79332</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B0D63FKYZ5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HM-01</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1638</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FBA79333</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B0D63DTKQB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HM-02</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1999</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FBA79346</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B0D25LNDSY</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ETC-04-WH</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="n">
+        <v>7788</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FBA79350</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B0D67727VG</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EA-01</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9495</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FBA79404</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B0D9KFZYG8</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FS-01</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FBA79406</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B0DCK3N2JJ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HSB-04</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2499</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FBA79452</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B0DCGHVN81</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VC-01</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3998</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FBA79467</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B0DK9LYT4P</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TM-01</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>899</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FBA79473</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B0DJFH6RTL</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TI-02</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3598</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FBA79590</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B0DM6BB3VT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CFM-01</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11996</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FBA79652</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SC-05</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>14495</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FBA79692</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>B0DVC58QPZ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AP-03</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FBA79819</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>B0FT8R24QM</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LR-03</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>23</v>
+      </c>
+      <c r="E20" t="n">
+        <v>11477</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FBK79271</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>B0DQ8W1RBV</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>V-01</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>11893</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ASIN</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sale Amount</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FBA78980</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B0CDPMX152</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GS-02</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>27094.38</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FBA78981</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>17105.28</v>
+        <v>15508.78</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -519,24 +1425,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FBA79332</t>
+          <t>FBA79271</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HM-01</t>
+          <t>V-01</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>27891.12</v>
+        <v>1284.7</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -547,24 +1453,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FBA79474</t>
+          <t>FBA79272</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TIC-03</t>
+          <t>HS-01</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>1919.86</v>
+        <v>2406</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -575,24 +1481,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FBA79483</t>
+          <t>FBA79273</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B0DK9NRBWJ</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>HS-02</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>38015.76</v>
+        <v>802</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -603,24 +1509,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FBA79488</t>
+          <t>FBA79348</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KE-01</t>
+          <t>HD-02</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E7" t="n">
-        <v>32066.5</v>
+        <v>26427</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -631,24 +1537,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FBA79566</t>
+          <t>FBA79439</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VC-05</t>
+          <t>MR-02</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>88910.64</v>
+        <v>5735.9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -659,24 +1565,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FBA79590</t>
+          <t>FBA79452</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CFM-01</t>
+          <t>VC-01</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>78273.60000000001</v>
+        <v>32471</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -687,24 +1593,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FBA79811</t>
+          <t>FBA79463</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B0FSF1N457</t>
+          <t>B0DCK56Q85</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MC-01</t>
+          <t>VC-02</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>12006.5</v>
+        <v>2069</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -715,26 +1621,194 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FBA79819</t>
+          <t>FBA79467</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B0FT8R24QM</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LR-03</t>
+          <t>TM-01</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FBA79469</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B0DCK4DR1B</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LE-04</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>903.1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FBA79472</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B0DFCDZWND</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CM-02-PR</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1284.7</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FBA79480</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B0DDC3GVZW</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VC-03</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="n">
-        <v>1283.84</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="E14" t="n">
+        <v>2698</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FBA79565</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B0DKJZDY72</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>VC-04</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1733.24</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FBA79566</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B0DKJSCLBD</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VC-05</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>7196</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FBK79271</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B0DQ8W1RBV</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>V-01</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1380.1</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/raw/sales/Week 33/Nexlev/other_channels.xlsx
+++ b/data/raw/sales/Week 33/Nexlev/other_channels.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,24 +465,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FBA79278</t>
+          <t>FBA78980</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HD-01</t>
+          <t>GS-02</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>4276.32</v>
+        <v>12259.58</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -493,24 +493,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FBA79332</t>
+          <t>FBA78981</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HM-01</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>4648.52</v>
+        <v>194915.22</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -521,24 +521,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FBA79474</t>
+          <t>FBA79234</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0CSG2JZ19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TIC-03</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1919.86</v>
+        <v>425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -549,24 +549,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FBA79483</t>
+          <t>FBA79267</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B0DK9NRBWJ</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TM-03</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>6335.96</v>
+        <v>1104</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -577,24 +577,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FBA79488</t>
+          <t>FBA79278</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KE-01</t>
+          <t>HD-01</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>6413.3</v>
+        <v>4900</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -605,24 +605,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FBA79566</t>
+          <t>FBA79332</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VC-05</t>
+          <t>HM-01</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>17098.2</v>
+        <v>5404.52</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -633,24 +633,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FBA79590</t>
+          <t>FBA79346</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CFM-01</t>
+          <t>ETC-04-WH</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>13045.6</v>
+        <v>6196.1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -661,24 +661,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FBA79811</t>
+          <t>FBA79373</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B0FSF1N457</t>
+          <t>B0D2P5TGWK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MC-01</t>
+          <t>ET-01-BK</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>2401.3</v>
+        <v>1936.27</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -689,26 +689,250 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>FBA79374</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B0D2P7WLJB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ET-02-GN</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1936.27</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FBA79474</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B0DJFH4K8B</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TIC-03</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1627</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FBA79483</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B0DK9NRBWJ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TM-03</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6335.96</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FBA79488</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B0DFCG2VGS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>KE-01</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5435</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FBA79566</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B0DKJSCLBD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VC-05</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16530</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FBA79590</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B0DM6BB3VT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CFM-01</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>13045.6</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FBA79707</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B0FJ1ZB4G9</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ETC-08-BL</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3863.05</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FBA79811</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B0FSF1N457</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MC-01</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2035</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>FBA79819</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>B0FT8R24QM</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>LR-03</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>641.92</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>926</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>
